--- a/data/gravel/Moots Routt 45 2025.xlsx
+++ b/data/gravel/Moots Routt 45 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655D5058-B96F-9D4B-9000-918075DAAA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740F73FE-82B9-B34A-AAE8-96E5371A1D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19700" yWindow="-17480" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="95">
   <si>
     <t>brand</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>https://moots.com/wp-content/uploads/2025/08/Routt-45-UDH-Trans-Am-1.jpg.webp</t>
   </si>
 </sst>
 </file>
@@ -701,6 +704,11 @@
         <v>91</v>
       </c>
     </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
+    </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Moots Routt 45 2025.xlsx
+++ b/data/gravel/Moots Routt 45 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740F73FE-82B9-B34A-AAE8-96E5371A1D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D86372-F973-5246-88AA-C21D72973628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
   <si>
     <t>brand</t>
   </si>
@@ -272,9 +272,6 @@
     <t>rider_max_spec</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>drop bar</t>
   </si>
   <si>
@@ -318,6 +315,15 @@
   </si>
   <si>
     <t>https://moots.com/wp-content/uploads/2025/08/Routt-45-UDH-Trans-Am-1.jpg.webp</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Steamboat Springs, Colorado, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -658,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -677,7 +683,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -701,12 +707,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -714,7 +720,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -722,7 +728,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8">
         <f>K8</f>
@@ -779,7 +785,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9">
         <f>K9*10</f>
@@ -836,7 +842,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10">
         <f t="shared" ref="C10:C11" si="2">K10*10</f>
@@ -893,7 +899,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11">
         <f t="shared" si="2"/>
@@ -1064,7 +1070,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14">
         <f t="shared" ref="C14:C15" si="4">K14*10</f>
@@ -1121,7 +1127,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C15">
         <f t="shared" si="4"/>
@@ -1178,7 +1184,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" s="3">
         <f>K16*25.4</f>
@@ -1652,7 +1658,7 @@
         <v>66</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -1660,7 +1666,7 @@
         <v>67</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1668,7 +1674,7 @@
         <v>68</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1803,7 +1809,7 @@
         <v>51</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -1895,7 +1901,15 @@
         <v>65</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>79</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>94</v>
+      </c>
+      <c r="B73" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Moots Routt 45 2025.xlsx
+++ b/data/gravel/Moots Routt 45 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D86372-F973-5246-88AA-C21D72973628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC97E5E4-813A-F845-9DE6-C3E590013A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="103">
   <si>
     <t>brand</t>
   </si>
@@ -324,6 +324,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -664,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1749,166 +1767,196 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51">
-        <v>27.2</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>49</v>
-      </c>
-      <c r="B56">
-        <v>160</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B57">
+        <v>27.2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>53</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>58</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>52</v>
+      </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>59</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>69</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>61</v>
-      </c>
-      <c r="B68" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>62</v>
-      </c>
-      <c r="B69" s="1">
-        <v>5999</v>
+        <v>56</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>63</v>
-      </c>
-      <c r="B70">
-        <v>8250</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B71" s="1"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74" s="1"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75" s="1">
+        <v>5999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B76">
+        <v>8250</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B77" s="1"/>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>94</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>95</v>
       </c>
     </row>

--- a/data/gravel/Moots Routt 45 2025.xlsx
+++ b/data/gravel/Moots Routt 45 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC97E5E4-813A-F845-9DE6-C3E590013A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72A9404-A348-8F47-9324-084411769364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -314,9 +314,6 @@
     <t>internal</t>
   </si>
   <si>
-    <t>https://moots.com/wp-content/uploads/2025/08/Routt-45-UDH-Trans-Am-1.jpg.webp</t>
-  </si>
-  <si>
     <t>location</t>
   </si>
   <si>
@@ -342,6 +339,9 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>https://moots.com/cdn/shop/files/Screenshot2025-10-16at3.32.05PM.png?v=1760650375&amp;width=2200</t>
   </si>
 </sst>
 </file>
@@ -730,7 +730,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -1767,32 +1767,32 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -1949,15 +1949,15 @@
         <v>65</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>93</v>
+      </c>
+      <c r="B79" t="s">
         <v>94</v>
-      </c>
-      <c r="B79" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
